--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="186">
   <si>
     <t>Código Produto</t>
   </si>
@@ -52,10 +52,232 @@
     <t>Fabricante</t>
   </si>
   <si>
-    <t>PROD001</t>
-  </si>
-  <si>
-    <t>Produto de Teste</t>
+    <t>PROD100002</t>
+  </si>
+  <si>
+    <t>PROD100005</t>
+  </si>
+  <si>
+    <t>PROD100008</t>
+  </si>
+  <si>
+    <t>PROD300001</t>
+  </si>
+  <si>
+    <t>PROD300002</t>
+  </si>
+  <si>
+    <t>PROD300003</t>
+  </si>
+  <si>
+    <t>PROD300004</t>
+  </si>
+  <si>
+    <t>PROD300005</t>
+  </si>
+  <si>
+    <t>PROD300006</t>
+  </si>
+  <si>
+    <t>PROD300011</t>
+  </si>
+  <si>
+    <t>PROD300012</t>
+  </si>
+  <si>
+    <t>PROD300013</t>
+  </si>
+  <si>
+    <t>PROD300014</t>
+  </si>
+  <si>
+    <t>PROD300015</t>
+  </si>
+  <si>
+    <t>PROD300016</t>
+  </si>
+  <si>
+    <t>PROD300017</t>
+  </si>
+  <si>
+    <t>PROD300018</t>
+  </si>
+  <si>
+    <t>PROD300019</t>
+  </si>
+  <si>
+    <t>PROD300020</t>
+  </si>
+  <si>
+    <t>PROD300021</t>
+  </si>
+  <si>
+    <t>PROD300022</t>
+  </si>
+  <si>
+    <t>PROD300023</t>
+  </si>
+  <si>
+    <t>PROD300024</t>
+  </si>
+  <si>
+    <t>PROD300025</t>
+  </si>
+  <si>
+    <t>PROD300026</t>
+  </si>
+  <si>
+    <t>PROD300027</t>
+  </si>
+  <si>
+    <t>PROD300028</t>
+  </si>
+  <si>
+    <t>PROD300029</t>
+  </si>
+  <si>
+    <t>PROD300030</t>
+  </si>
+  <si>
+    <t>PROD400001</t>
+  </si>
+  <si>
+    <t>PROD400002</t>
+  </si>
+  <si>
+    <t>PROD400003</t>
+  </si>
+  <si>
+    <t>PROD500001</t>
+  </si>
+  <si>
+    <t>PROD500002</t>
+  </si>
+  <si>
+    <t>PROD500003</t>
+  </si>
+  <si>
+    <t>PROD500004</t>
+  </si>
+  <si>
+    <t>PROD500005</t>
+  </si>
+  <si>
+    <t>PROD500006</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100005</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100008</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300003</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300004</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300005</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300006</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300011</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300012</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300013</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300014</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300015</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300016</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300017</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300018</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300019</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300020</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300021</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300022</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300023</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300024</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300025</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300026</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300027</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300028</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300029</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300030</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400003</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500003</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500004</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500005</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500006</t>
   </si>
   <si>
     <t>100002</t>
@@ -67,7 +289,109 @@
     <t>100008</t>
   </si>
   <si>
-    <t>100009</t>
+    <t>300001</t>
+  </si>
+  <si>
+    <t>300002</t>
+  </si>
+  <si>
+    <t>300003</t>
+  </si>
+  <si>
+    <t>300004</t>
+  </si>
+  <si>
+    <t>300005</t>
+  </si>
+  <si>
+    <t>300006</t>
+  </si>
+  <si>
+    <t>300011</t>
+  </si>
+  <si>
+    <t>300012</t>
+  </si>
+  <si>
+    <t>300013</t>
+  </si>
+  <si>
+    <t>300014</t>
+  </si>
+  <si>
+    <t>300015</t>
+  </si>
+  <si>
+    <t>300016</t>
+  </si>
+  <si>
+    <t>300017</t>
+  </si>
+  <si>
+    <t>300018</t>
+  </si>
+  <si>
+    <t>300019</t>
+  </si>
+  <si>
+    <t>300020</t>
+  </si>
+  <si>
+    <t>300021</t>
+  </si>
+  <si>
+    <t>300022</t>
+  </si>
+  <si>
+    <t>300023</t>
+  </si>
+  <si>
+    <t>300024</t>
+  </si>
+  <si>
+    <t>300025</t>
+  </si>
+  <si>
+    <t>300026</t>
+  </si>
+  <si>
+    <t>300027</t>
+  </si>
+  <si>
+    <t>300028</t>
+  </si>
+  <si>
+    <t>300029</t>
+  </si>
+  <si>
+    <t>300030</t>
+  </si>
+  <si>
+    <t>400001</t>
+  </si>
+  <si>
+    <t>400002</t>
+  </si>
+  <si>
+    <t>400003</t>
+  </si>
+  <si>
+    <t>500001</t>
+  </si>
+  <si>
+    <t>500002</t>
+  </si>
+  <si>
+    <t>500003</t>
+  </si>
+  <si>
+    <t>500004</t>
+  </si>
+  <si>
+    <t>500005</t>
+  </si>
+  <si>
+    <t>500006</t>
   </si>
   <si>
     <t>15000</t>
@@ -79,25 +403,142 @@
     <t>50000</t>
   </si>
   <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>15500</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>16500</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>17500</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>18500</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>19500</t>
+  </si>
+  <si>
+    <t>20500</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>21500</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>22500</t>
+  </si>
+  <si>
+    <t>23000</t>
+  </si>
+  <si>
+    <t>23500</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>24500</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
     <t>8000</t>
   </si>
   <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>28000</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
     <t>Alessandro Cappi</t>
   </si>
   <si>
     <t>André Caramello</t>
   </si>
   <si>
+    <t>Andrey Andrade</t>
+  </si>
+  <si>
+    <t>Mateus Machado</t>
+  </si>
+  <si>
+    <t>André Camargo</t>
+  </si>
+  <si>
+    <t>Leonardo Carmo</t>
+  </si>
+  <si>
     <t>Produto</t>
   </si>
   <si>
+    <t>Aluguel</t>
+  </si>
+  <si>
+    <t>Reposição</t>
+  </si>
+  <si>
+    <t>Serviço</t>
+  </si>
+  <si>
     <t>Falco</t>
   </si>
   <si>
     <t>Acessório</t>
   </si>
   <si>
-    <t>Titan</t>
+    <t>ISCO</t>
+  </si>
+  <si>
+    <t>QED</t>
+  </si>
+  <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>Thermo</t>
+  </si>
+  <si>
+    <t>YSI</t>
   </si>
   <si>
     <t>Analisador Fixo</t>
@@ -106,7 +547,31 @@
     <t>Analisador Portátil</t>
   </si>
   <si>
+    <t>Equipamento Amostragem</t>
+  </si>
+  <si>
+    <t>Sistema Remediação</t>
+  </si>
+  <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>Sonda Multiparâmetros</t>
+  </si>
+  <si>
     <t>SSO</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
+  </si>
+  <si>
+    <t>Remediação</t>
+  </si>
+  <si>
+    <t>HON</t>
+  </si>
+  <si>
+    <t>ION</t>
   </si>
 </sst>
 </file>
@@ -468,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -514,127 +979,1399 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2">
         <v>45894</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2">
         <v>45889</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2">
         <v>45884</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>157</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2">
+        <v>45884</v>
+      </c>
+      <c r="E5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" t="s">
+        <v>175</v>
+      </c>
+      <c r="K5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="2">
+        <v>45887</v>
+      </c>
+      <c r="E6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I6" t="s">
+        <v>169</v>
+      </c>
+      <c r="J6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2">
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45891</v>
+      </c>
+      <c r="E8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" t="s">
+        <v>163</v>
+      </c>
+      <c r="I8" t="s">
+        <v>171</v>
+      </c>
+      <c r="J8" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="2">
+        <v>45894</v>
+      </c>
+      <c r="E9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G9" t="s">
+        <v>161</v>
+      </c>
+      <c r="H9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I9" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="2">
+        <v>45897</v>
+      </c>
+      <c r="E10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10" t="s">
+        <v>167</v>
+      </c>
+      <c r="J10" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="2">
+        <v>45897</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="2">
+        <v>45885</v>
+      </c>
+      <c r="E12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J12" t="s">
+        <v>175</v>
+      </c>
+      <c r="K12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="2">
+        <v>45886</v>
+      </c>
+      <c r="E13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" t="s">
+        <v>167</v>
+      </c>
+      <c r="J13" t="s">
+        <v>175</v>
+      </c>
+      <c r="K13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="2">
         <v>45887</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" t="s">
+        <v>175</v>
+      </c>
+      <c r="K14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="I5" t="s">
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="2">
+        <v>45888</v>
+      </c>
+      <c r="E15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" t="s">
+        <v>175</v>
+      </c>
+      <c r="K15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" t="s">
+        <v>175</v>
+      </c>
+      <c r="K16" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="2">
+        <v>45890</v>
+      </c>
+      <c r="E17" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" t="s">
+        <v>167</v>
+      </c>
+      <c r="J17" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
+      <c r="B18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="2">
+        <v>45891</v>
+      </c>
+      <c r="E18" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" t="s">
+        <v>165</v>
+      </c>
+      <c r="I18" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" t="s">
+        <v>175</v>
+      </c>
+      <c r="K18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="K5" t="s">
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="2">
+        <v>45892</v>
+      </c>
+      <c r="E19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F19" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" t="s">
+        <v>166</v>
+      </c>
+      <c r="I19" t="s">
+        <v>167</v>
+      </c>
+      <c r="J19" t="s">
+        <v>175</v>
+      </c>
+      <c r="K19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="2">
+        <v>45893</v>
+      </c>
+      <c r="E20" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" t="s">
+        <v>159</v>
+      </c>
+      <c r="H20" t="s">
+        <v>164</v>
+      </c>
+      <c r="I20" t="s">
+        <v>167</v>
+      </c>
+      <c r="J20" t="s">
+        <v>175</v>
+      </c>
+      <c r="K20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="2">
+        <v>45894</v>
+      </c>
+      <c r="E21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" t="s">
+        <v>175</v>
+      </c>
+      <c r="K21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="2">
+        <v>45895</v>
+      </c>
+      <c r="E22" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" t="s">
+        <v>165</v>
+      </c>
+      <c r="I22" t="s">
+        <v>167</v>
+      </c>
+      <c r="J22" t="s">
+        <v>175</v>
+      </c>
+      <c r="K22" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2">
+        <v>45896</v>
+      </c>
+      <c r="E23" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J23" t="s">
+        <v>175</v>
+      </c>
+      <c r="K23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="2">
+        <v>45897</v>
+      </c>
+      <c r="E24" t="s">
+        <v>143</v>
+      </c>
+      <c r="F24" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" t="s">
+        <v>164</v>
+      </c>
+      <c r="I24" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24" t="s">
+        <v>175</v>
+      </c>
+      <c r="K24" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="2">
+        <v>45898</v>
+      </c>
+      <c r="E25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" t="s">
+        <v>159</v>
+      </c>
+      <c r="H25" t="s">
+        <v>163</v>
+      </c>
+      <c r="I25" t="s">
+        <v>167</v>
+      </c>
+      <c r="J25" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45874</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" t="s">
+        <v>165</v>
+      </c>
+      <c r="I26" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" t="s">
+        <v>175</v>
+      </c>
+      <c r="K26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45875</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" t="s">
+        <v>167</v>
+      </c>
+      <c r="J27" t="s">
+        <v>175</v>
+      </c>
+      <c r="K27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="2">
+        <v>45876</v>
+      </c>
+      <c r="E28" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" t="s">
+        <v>164</v>
+      </c>
+      <c r="I28" t="s">
+        <v>167</v>
+      </c>
+      <c r="J28" t="s">
+        <v>175</v>
+      </c>
+      <c r="K28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45877</v>
+      </c>
+      <c r="E29" t="s">
+        <v>148</v>
+      </c>
+      <c r="F29" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" t="s">
+        <v>167</v>
+      </c>
+      <c r="J29" t="s">
+        <v>175</v>
+      </c>
+      <c r="K29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="2">
+        <v>45878</v>
+      </c>
+      <c r="E30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" t="s">
+        <v>159</v>
+      </c>
+      <c r="H30" t="s">
+        <v>165</v>
+      </c>
+      <c r="I30" t="s">
+        <v>167</v>
+      </c>
+      <c r="J30" t="s">
+        <v>175</v>
+      </c>
+      <c r="K30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="2">
+        <v>45879</v>
+      </c>
+      <c r="E31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F31" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" t="s">
+        <v>167</v>
+      </c>
+      <c r="J31" t="s">
+        <v>175</v>
+      </c>
+      <c r="K31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45879</v>
+      </c>
+      <c r="E32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32" t="s">
+        <v>163</v>
+      </c>
+      <c r="I32" t="s">
+        <v>167</v>
+      </c>
+      <c r="J32" t="s">
+        <v>175</v>
+      </c>
+      <c r="K32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="2">
+        <v>45879</v>
+      </c>
+      <c r="E33" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" t="s">
+        <v>163</v>
+      </c>
+      <c r="I33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J33" t="s">
+        <v>177</v>
+      </c>
+      <c r="K33" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="2">
+        <v>45884</v>
+      </c>
+      <c r="E34" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" t="s">
+        <v>163</v>
+      </c>
+      <c r="I34" t="s">
+        <v>171</v>
+      </c>
+      <c r="J34" t="s">
+        <v>179</v>
+      </c>
+      <c r="K34" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="2">
+        <v>45884</v>
+      </c>
+      <c r="E35" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>160</v>
+      </c>
+      <c r="H35" t="s">
+        <v>163</v>
+      </c>
+      <c r="I35" t="s">
+        <v>170</v>
+      </c>
+      <c r="J35" t="s">
+        <v>178</v>
+      </c>
+      <c r="K35" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" t="s">
+        <v>159</v>
+      </c>
+      <c r="H36" t="s">
+        <v>163</v>
+      </c>
+      <c r="I36" t="s">
+        <v>172</v>
+      </c>
+      <c r="J36" t="s">
+        <v>180</v>
+      </c>
+      <c r="K36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E37" t="s">
+        <v>152</v>
+      </c>
+      <c r="F37" t="s">
+        <v>159</v>
+      </c>
+      <c r="H37" t="s">
+        <v>163</v>
+      </c>
+      <c r="I37" t="s">
+        <v>167</v>
+      </c>
+      <c r="J37" t="s">
+        <v>175</v>
+      </c>
+      <c r="K37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" t="s">
+        <v>159</v>
+      </c>
+      <c r="H38" t="s">
+        <v>163</v>
+      </c>
+      <c r="I38" t="s">
+        <v>173</v>
+      </c>
+      <c r="J38" t="s">
+        <v>178</v>
+      </c>
+      <c r="K38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="2">
+        <v>45877</v>
+      </c>
+      <c r="E39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H39" t="s">
+        <v>163</v>
+      </c>
+      <c r="I39" t="s">
+        <v>174</v>
+      </c>
+      <c r="J39" t="s">
+        <v>177</v>
+      </c>
+      <c r="K39" t="s">
+        <v>182</v>
+      </c>
+      <c r="L39" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="2">
+        <v>45880</v>
+      </c>
+      <c r="E40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" t="s">
+        <v>157</v>
+      </c>
+      <c r="H40" t="s">
+        <v>163</v>
+      </c>
+      <c r="I40" t="s">
+        <v>169</v>
+      </c>
+      <c r="J40" t="s">
+        <v>177</v>
+      </c>
+      <c r="K40" t="s">
+        <v>182</v>
+      </c>
+      <c r="L40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" s="2">
+        <v>45883</v>
+      </c>
+      <c r="E41" t="s">
+        <v>153</v>
+      </c>
+      <c r="F41" t="s">
+        <v>157</v>
+      </c>
+      <c r="H41" t="s">
+        <v>163</v>
+      </c>
+      <c r="I41" t="s">
+        <v>170</v>
+      </c>
+      <c r="J41" t="s">
+        <v>178</v>
+      </c>
+      <c r="K41" t="s">
+        <v>183</v>
+      </c>
+      <c r="L41" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="2">
+        <v>45886</v>
+      </c>
+      <c r="E42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F42" t="s">
+        <v>157</v>
+      </c>
+      <c r="H42" t="s">
+        <v>163</v>
+      </c>
+      <c r="I42" t="s">
+        <v>173</v>
+      </c>
+      <c r="J42" t="s">
+        <v>178</v>
+      </c>
+      <c r="K42" t="s">
+        <v>183</v>
+      </c>
+      <c r="L42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E43" t="s">
+        <v>155</v>
+      </c>
+      <c r="F43" t="s">
+        <v>157</v>
+      </c>
+      <c r="H43" t="s">
+        <v>163</v>
+      </c>
+      <c r="I43" t="s">
+        <v>167</v>
+      </c>
+      <c r="J43" t="s">
+        <v>175</v>
+      </c>
+      <c r="K43" t="s">
+        <v>181</v>
+      </c>
+      <c r="L43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="2">
+        <v>45892</v>
+      </c>
+      <c r="E44" t="s">
+        <v>156</v>
+      </c>
+      <c r="F44" t="s">
+        <v>157</v>
+      </c>
+      <c r="H44" t="s">
+        <v>163</v>
+      </c>
+      <c r="I44" t="s">
+        <v>171</v>
+      </c>
+      <c r="J44" t="s">
+        <v>179</v>
+      </c>
+      <c r="K44" t="s">
+        <v>181</v>
+      </c>
+      <c r="L44" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="194">
   <si>
     <t>Código Produto</t>
   </si>
@@ -148,6 +148,9 @@
     <t>PROD400003</t>
   </si>
   <si>
+    <t>PROD400004</t>
+  </si>
+  <si>
     <t>PROD500001</t>
   </si>
   <si>
@@ -262,6 +265,9 @@
     <t>Produto de Teste - Processo 400003</t>
   </si>
   <si>
+    <t>Produto de Teste - Processo 400004</t>
+  </si>
+  <si>
     <t>Produto de Teste - Processo 500001</t>
   </si>
   <si>
@@ -376,6 +382,9 @@
     <t>400003</t>
   </si>
   <si>
+    <t>400004</t>
+  </si>
+  <si>
     <t>500001</t>
   </si>
   <si>
@@ -487,22 +496,28 @@
     <t>32000</t>
   </si>
   <si>
-    <t>Alessandro Cappi</t>
-  </si>
-  <si>
-    <t>André Caramello</t>
-  </si>
-  <si>
-    <t>Andrey Andrade</t>
-  </si>
-  <si>
-    <t>Mateus Machado</t>
-  </si>
-  <si>
-    <t>André Camargo</t>
-  </si>
-  <si>
-    <t>Leonardo Carmo</t>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>JULIANO</t>
+  </si>
+  <si>
+    <t>ROSANA.MARTINS</t>
+  </si>
+  <si>
+    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
+  </si>
+  <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>LEONARDO DO CARMO</t>
   </si>
   <si>
     <t>Produto</t>
@@ -526,21 +541,27 @@
     <t>ISCO</t>
   </si>
   <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>E3 Point</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
     <t>QED</t>
   </si>
   <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
-    <t>EXO</t>
+    <t>Panther</t>
+  </si>
+  <si>
+    <t>YSI</t>
   </si>
   <si>
     <t>Thermo</t>
   </si>
   <si>
-    <t>YSI</t>
-  </si>
-  <si>
     <t>Analisador Fixo</t>
   </si>
   <si>
@@ -550,13 +571,16 @@
     <t>Equipamento Amostragem</t>
   </si>
   <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
+    <t>Sonda Multiparâmetros</t>
+  </si>
+  <si>
     <t>Sistema Remediação</t>
-  </si>
-  <si>
-    <t>Detector Portátil</t>
-  </si>
-  <si>
-    <t>Sonda Multiparâmetros</t>
   </si>
   <si>
     <t>SSO</t>
@@ -933,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -979,31 +1003,28 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2">
         <v>45894</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="H2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1011,31 +1032,28 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" s="2">
         <v>45889</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J3" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="K3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1043,31 +1061,28 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" s="2">
         <v>45884</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F4" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="H4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K4" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1075,31 +1090,34 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" s="2">
         <v>45884</v>
       </c>
       <c r="E5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F5" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="G5" t="s">
+        <v>165</v>
       </c>
       <c r="H5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I5" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1107,34 +1125,34 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2">
         <v>45887</v>
       </c>
       <c r="E6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J6" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1142,31 +1160,31 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2">
         <v>45889</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J7" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="K7" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1174,31 +1192,31 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" s="2">
         <v>45891</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H8" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I8" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J8" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="K8" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1206,34 +1224,34 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2">
         <v>45894</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G9" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K9" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1241,31 +1259,34 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2">
         <v>45897</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F10" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="G10" t="s">
+        <v>165</v>
       </c>
       <c r="H10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I10" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1273,31 +1294,34 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="2">
         <v>45897</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F11" t="s">
         <v>160</v>
       </c>
+      <c r="G11" t="s">
+        <v>165</v>
+      </c>
       <c r="H11" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="K11" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1305,31 +1329,28 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2">
         <v>45885</v>
       </c>
       <c r="E12" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="H12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I12" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J12" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K12" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1337,31 +1358,34 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2">
         <v>45886</v>
       </c>
       <c r="E13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F13" t="s">
-        <v>159</v>
+        <v>162</v>
+      </c>
+      <c r="G13" t="s">
+        <v>165</v>
       </c>
       <c r="H13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I13" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J13" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K13" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1369,31 +1393,31 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" s="2">
         <v>45887</v>
       </c>
       <c r="E14" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" t="s">
-        <v>159</v>
+        <v>137</v>
+      </c>
+      <c r="G14" t="s">
+        <v>166</v>
       </c>
       <c r="H14" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I14" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K14" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1401,31 +1425,34 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D15" s="2">
         <v>45888</v>
       </c>
       <c r="E15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F15" t="s">
-        <v>159</v>
+        <v>163</v>
+      </c>
+      <c r="G15" t="s">
+        <v>166</v>
       </c>
       <c r="H15" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I15" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K15" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1433,31 +1460,28 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" s="2">
         <v>45889</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="H16" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I16" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K16" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1465,31 +1489,34 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D17" s="2">
         <v>45890</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F17" t="s">
-        <v>159</v>
+        <v>161</v>
+      </c>
+      <c r="G17" t="s">
+        <v>166</v>
       </c>
       <c r="H17" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I17" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J17" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K17" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1497,31 +1524,31 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D18" s="2">
         <v>45891</v>
       </c>
       <c r="E18" t="s">
-        <v>138</v>
-      </c>
-      <c r="F18" t="s">
-        <v>159</v>
+        <v>141</v>
+      </c>
+      <c r="G18" t="s">
+        <v>167</v>
       </c>
       <c r="H18" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I18" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J18" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K18" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1529,31 +1556,34 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" s="2">
         <v>45892</v>
       </c>
       <c r="E19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F19" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="G19" t="s">
+        <v>165</v>
       </c>
       <c r="H19" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I19" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K19" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1561,31 +1591,28 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D20" s="2">
         <v>45893</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="H20" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I20" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J20" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K20" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1593,31 +1620,34 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D21" s="2">
         <v>45894</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F21" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="G21" t="s">
+        <v>165</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I21" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J21" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K21" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1625,31 +1655,31 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D22" s="2">
         <v>45895</v>
       </c>
       <c r="E22" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" t="s">
-        <v>159</v>
+        <v>144</v>
+      </c>
+      <c r="G22" t="s">
+        <v>167</v>
       </c>
       <c r="H22" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I22" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K22" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1657,31 +1687,34 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D23" s="2">
         <v>45896</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F23" t="s">
-        <v>159</v>
+        <v>162</v>
+      </c>
+      <c r="G23" t="s">
+        <v>166</v>
       </c>
       <c r="H23" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I23" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J23" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K23" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1689,31 +1722,28 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D24" s="2">
         <v>45897</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
-      </c>
-      <c r="F24" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="H24" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I24" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K24" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1721,31 +1751,34 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D25" s="2">
         <v>45898</v>
       </c>
       <c r="E25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F25" t="s">
-        <v>159</v>
+        <v>163</v>
+      </c>
+      <c r="G25" t="s">
+        <v>165</v>
       </c>
       <c r="H25" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K25" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1753,31 +1786,31 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D26" s="2">
         <v>45874</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
-      </c>
-      <c r="F26" t="s">
-        <v>159</v>
+        <v>148</v>
+      </c>
+      <c r="G26" t="s">
+        <v>166</v>
       </c>
       <c r="H26" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I26" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J26" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K26" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1785,31 +1818,34 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D27" s="2">
         <v>45875</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>161</v>
+      </c>
+      <c r="G27" t="s">
+        <v>166</v>
       </c>
       <c r="H27" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I27" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J27" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K27" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1817,31 +1853,28 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D28" s="2">
         <v>45876</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H28" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I28" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K28" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1849,31 +1882,34 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D29" s="2">
         <v>45877</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="G29" t="s">
+        <v>166</v>
       </c>
       <c r="H29" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I29" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J29" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K29" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1881,31 +1917,31 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D30" s="2">
         <v>45878</v>
       </c>
       <c r="E30" t="s">
-        <v>149</v>
-      </c>
-      <c r="F30" t="s">
-        <v>159</v>
+        <v>152</v>
+      </c>
+      <c r="G30" t="s">
+        <v>167</v>
       </c>
       <c r="H30" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J30" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K30" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1913,31 +1949,34 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D31" s="2">
         <v>45879</v>
       </c>
       <c r="E31" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="G31" t="s">
+        <v>165</v>
       </c>
       <c r="H31" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="I31" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J31" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K31" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1945,31 +1984,31 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D32" s="2">
         <v>45879</v>
       </c>
       <c r="E32" t="s">
-        <v>150</v>
-      </c>
-      <c r="F32" t="s">
-        <v>159</v>
+        <v>153</v>
+      </c>
+      <c r="G32" t="s">
+        <v>165</v>
       </c>
       <c r="H32" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I32" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J32" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K32" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1977,31 +2016,28 @@
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D33" s="2">
         <v>45879</v>
       </c>
       <c r="E33" t="s">
-        <v>151</v>
-      </c>
-      <c r="F33" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H33" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J33" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K33" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2009,31 +2045,31 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D34" s="2">
         <v>45884</v>
       </c>
       <c r="E34" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" t="s">
-        <v>160</v>
+        <v>130</v>
+      </c>
+      <c r="G34" t="s">
+        <v>166</v>
       </c>
       <c r="H34" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J34" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="K34" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2041,31 +2077,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D35" s="2">
         <v>45884</v>
       </c>
       <c r="E35" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H35" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I35" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J35" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="K35" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2073,31 +2106,31 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D36" s="2">
         <v>45889</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" t="s">
-        <v>159</v>
+        <v>129</v>
+      </c>
+      <c r="G36" t="s">
+        <v>167</v>
       </c>
       <c r="H36" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I36" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="J36" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K36" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2105,31 +2138,28 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D37" s="2">
         <v>45889</v>
       </c>
       <c r="E37" t="s">
-        <v>152</v>
-      </c>
-      <c r="F37" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H37" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="J37" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K37" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2137,31 +2167,28 @@
         <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D38" s="2">
         <v>45889</v>
       </c>
       <c r="E38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F38" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H38" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I38" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J38" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K38" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2169,209 +2196,267 @@
         <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D39" s="2">
-        <v>45877</v>
+        <v>45894</v>
       </c>
       <c r="E39" t="s">
-        <v>129</v>
-      </c>
-      <c r="F39" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J39" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="K39" t="s">
-        <v>182</v>
-      </c>
-      <c r="L39" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
         <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D40" s="2">
-        <v>45880</v>
+        <v>45894</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
-      </c>
-      <c r="F40" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="H40" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J40" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="K40" t="s">
-        <v>182</v>
-      </c>
-      <c r="L40" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
         <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" s="2">
-        <v>45883</v>
+        <v>45877</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="F41" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H41" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I41" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="J41" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K41" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="L41" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
         <v>85</v>
       </c>
       <c r="C42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D42" s="2">
-        <v>45886</v>
+        <v>45880</v>
       </c>
       <c r="E42" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="F42" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H42" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J42" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K42" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
         <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D43" s="2">
-        <v>45889</v>
+        <v>45883</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F43" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H43" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I43" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J43" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="K43" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L43" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
         <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D44" s="2">
+        <v>45886</v>
+      </c>
+      <c r="E44" t="s">
+        <v>157</v>
+      </c>
+      <c r="F44" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" t="s">
+        <v>168</v>
+      </c>
+      <c r="I44" t="s">
+        <v>181</v>
+      </c>
+      <c r="J44" t="s">
+        <v>188</v>
+      </c>
+      <c r="K44" t="s">
+        <v>191</v>
+      </c>
+      <c r="L44" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" s="2">
+        <v>45889</v>
+      </c>
+      <c r="E45" t="s">
+        <v>158</v>
+      </c>
+      <c r="F45" t="s">
+        <v>160</v>
+      </c>
+      <c r="H45" t="s">
+        <v>168</v>
+      </c>
+      <c r="I45" t="s">
+        <v>172</v>
+      </c>
+      <c r="J45" t="s">
+        <v>182</v>
+      </c>
+      <c r="K45" t="s">
+        <v>189</v>
+      </c>
+      <c r="L45" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="2">
         <v>45892</v>
       </c>
-      <c r="E44" t="s">
-        <v>156</v>
-      </c>
-      <c r="F44" t="s">
-        <v>157</v>
-      </c>
-      <c r="H44" t="s">
-        <v>163</v>
-      </c>
-      <c r="I44" t="s">
-        <v>171</v>
-      </c>
-      <c r="J44" t="s">
-        <v>179</v>
-      </c>
-      <c r="K44" t="s">
-        <v>181</v>
-      </c>
-      <c r="L44" t="s">
+      <c r="E46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" t="s">
+        <v>168</v>
+      </c>
+      <c r="I46" t="s">
+        <v>175</v>
+      </c>
+      <c r="J46" t="s">
         <v>185</v>
+      </c>
+      <c r="K46" t="s">
+        <v>189</v>
+      </c>
+      <c r="L46" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -403,13 +403,13 @@
     <t>500006</t>
   </si>
   <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>48000</t>
-  </si>
-  <si>
-    <t>150000</t>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>16000</t>
   </si>
   <si>
     <t>50000</t>
@@ -427,79 +427,79 @@
     <t>25000</t>
   </si>
   <si>
-    <t>20500</t>
-  </si>
-  <si>
-    <t>21000</t>
-  </si>
-  <si>
-    <t>21500</t>
-  </si>
-  <si>
-    <t>22000</t>
-  </si>
-  <si>
-    <t>22500</t>
-  </si>
-  <si>
-    <t>23000</t>
-  </si>
-  <si>
-    <t>23500</t>
-  </si>
-  <si>
-    <t>24000</t>
-  </si>
-  <si>
-    <t>24500</t>
-  </si>
-  <si>
-    <t>25500</t>
-  </si>
-  <si>
-    <t>26000</t>
-  </si>
-  <si>
-    <t>26500</t>
-  </si>
-  <si>
-    <t>27000</t>
-  </si>
-  <si>
-    <t>27500</t>
+    <t>7400</t>
+  </si>
+  <si>
+    <t>7800</t>
+  </si>
+  <si>
+    <t>8200</t>
+  </si>
+  <si>
+    <t>8600</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>9400</t>
+  </si>
+  <si>
+    <t>9800</t>
+  </si>
+  <si>
+    <t>10200</t>
+  </si>
+  <si>
+    <t>10600</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>11400</t>
+  </si>
+  <si>
+    <t>11800</t>
+  </si>
+  <si>
+    <t>12200</t>
+  </si>
+  <si>
+    <t>12600</t>
+  </si>
+  <si>
+    <t>13000</t>
+  </si>
+  <si>
+    <t>13400</t>
+  </si>
+  <si>
+    <t>13800</t>
+  </si>
+  <si>
+    <t>14200</t>
+  </si>
+  <si>
+    <t>14600</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>40000</t>
   </si>
   <si>
     <t>28000</t>
-  </si>
-  <si>
-    <t>28500</t>
-  </si>
-  <si>
-    <t>29000</t>
-  </si>
-  <si>
-    <t>29500</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>8000</t>
-  </si>
-  <si>
-    <t>12000</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>40000</t>
   </si>
   <si>
     <t>32000</t>
@@ -1689,7 +1689,7 @@
         <v>45894</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F21" t="s">
         <v>163</v>
@@ -1724,7 +1724,7 @@
         <v>45895</v>
       </c>
       <c r="E22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F22" t="s">
         <v>163</v>
@@ -1759,7 +1759,7 @@
         <v>45896</v>
       </c>
       <c r="E23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F23" t="s">
         <v>165</v>
@@ -1794,7 +1794,7 @@
         <v>45897</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F24" t="s">
         <v>166</v>
@@ -1829,7 +1829,7 @@
         <v>45898</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
         <v>167</v>
@@ -1864,7 +1864,7 @@
         <v>45874</v>
       </c>
       <c r="E26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F26" t="s">
         <v>165</v>
@@ -1899,7 +1899,7 @@
         <v>45875</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
         <v>164</v>
@@ -1934,7 +1934,7 @@
         <v>45876</v>
       </c>
       <c r="E28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F28" t="s">
         <v>163</v>
@@ -1969,7 +1969,7 @@
         <v>45877</v>
       </c>
       <c r="E29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F29" t="s">
         <v>168</v>
@@ -2004,7 +2004,7 @@
         <v>45878</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F30" t="s">
         <v>166</v>
@@ -2039,7 +2039,7 @@
         <v>45879</v>
       </c>
       <c r="E31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s">
         <v>163</v>
@@ -2074,7 +2074,7 @@
         <v>45879</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
         <v>167</v>
@@ -2141,7 +2141,7 @@
         <v>45884</v>
       </c>
       <c r="E34" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="F34" t="s">
         <v>164</v>
@@ -2176,7 +2176,7 @@
         <v>45884</v>
       </c>
       <c r="E35" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="F35" t="s">
         <v>163</v>
@@ -2243,7 +2243,7 @@
         <v>45889</v>
       </c>
       <c r="E37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F37" t="s">
         <v>165</v>
@@ -2307,7 +2307,7 @@
         <v>45894</v>
       </c>
       <c r="E39" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F39" t="s">
         <v>164</v>
@@ -2339,7 +2339,7 @@
         <v>45894</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="F40" t="s">
         <v>164</v>
@@ -2447,7 +2447,7 @@
         <v>45883</v>
       </c>
       <c r="E43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43" t="s">
         <v>163</v>
@@ -2485,7 +2485,7 @@
         <v>45886</v>
       </c>
       <c r="E44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F44" t="s">
         <v>163</v>
@@ -2523,7 +2523,7 @@
         <v>45889</v>
       </c>
       <c r="E45" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F45" t="s">
         <v>163</v>

--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -1,40 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+  <si>
+    <t>Código Produto</t>
+  </si>
+  <si>
+    <t>Descrição Produto</t>
+  </si>
+  <si>
+    <t>Processo</t>
+  </si>
+  <si>
+    <t>Dt Emissão</t>
+  </si>
+  <si>
+    <t>Valor Realizado</t>
+  </si>
+  <si>
+    <t>Consultor Interno</t>
+  </si>
+  <si>
+    <t>Representante-pedido</t>
+  </si>
+  <si>
+    <t>Tipo de Mercadoria</t>
+  </si>
+  <si>
+    <t>Subgrupo</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Negócio</t>
+  </si>
+  <si>
+    <t>Fabricante</t>
+  </si>
+  <si>
+    <t>PROD100002</t>
+  </si>
+  <si>
+    <t>PROD400001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400001</t>
+  </si>
+  <si>
+    <t>100002</t>
+  </si>
+  <si>
+    <t>400001</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
+  </si>
+  <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>XCD</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
+    <t>Medidor de Vazão Fixo</t>
+  </si>
+  <si>
+    <t>SSO</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +159,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -424,245 +476,154 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Código Produto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descrição Produto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Dt Emissão</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Realizado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Representante-pedido</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Mercadoria</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Subgrupo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Negócio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fabricante</t>
-        </is>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>100002</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2">
         <v>45894</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ANDREY.ANDRADE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PROD100002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 100002</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>100002</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2">
         <v>45894</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ANDREY.ANDRADE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>XCD</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Detector Fixo</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PROD400001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Produto de Teste - Processo 400001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>400001</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2">
         <v>45879</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>SAMANTA</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MATEUS BORRO MACHADO</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ADP</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Medidor de Vazão Fixo</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Hidrologia</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>Código Produto</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>400001</t>
+  </si>
+  <si>
+    <t>100001</t>
   </si>
   <si>
     <t>50</t>
@@ -477,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -532,25 +535,25 @@
         <v>45894</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -567,25 +570,25 @@
         <v>45894</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -602,24 +605,59 @@
         <v>45879</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2">
+        <v>45879</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>24</v>
       </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Código Produto</t>
   </si>
@@ -52,73 +52,43 @@
     <t>Fabricante</t>
   </si>
   <si>
-    <t>PROD100002</t>
-  </si>
-  <si>
-    <t>PROD400001</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 100002</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 400001</t>
-  </si>
-  <si>
-    <t>100002</t>
-  </si>
-  <si>
-    <t>400001</t>
-  </si>
-  <si>
-    <t>100001</t>
-  </si>
-  <si>
-    <t>50</t>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>TESTE2</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>ANDREY.ANDRADE</t>
-  </si>
-  <si>
     <t>SAMANTA</t>
   </si>
   <si>
-    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
-  </si>
-  <si>
     <t>MATEUS BORRO MACHADO</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
-    <t>XCD</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>Detector Portátil</t>
-  </si>
-  <si>
-    <t>Detector Fixo</t>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>IQ Standard</t>
+  </si>
+  <si>
+    <t>Sonda Serie EXO</t>
   </si>
   <si>
     <t>Medidor de Vazão Fixo</t>
   </si>
   <si>
-    <t>SSO</t>
-  </si>
-  <si>
     <t>Hidrologia</t>
+  </si>
+  <si>
+    <t>YSI</t>
   </si>
 </sst>
 </file>
@@ -480,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -522,143 +492,99 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" s="2">
+        <v>45931</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2">
-        <v>45894</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
         <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2">
+        <v>45931</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2">
-        <v>45894</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2">
+        <v>45941</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2">
-        <v>45879</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="K4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2">
-        <v>45879</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="L4" t="s">
         <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>Código Produto</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>Fabricante</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>BBB</t>
   </si>
   <si>
     <t>TESTE</t>
@@ -492,99 +498,108 @@
       </c>
     </row>
     <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
         <v>45931</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
         <v>45931</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2">
         <v>45941</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -1,135 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
-  <si>
-    <t>Código Produto</t>
-  </si>
-  <si>
-    <t>Descrição Produto</t>
-  </si>
-  <si>
-    <t>Processo</t>
-  </si>
-  <si>
-    <t>Dt Emissão</t>
-  </si>
-  <si>
-    <t>Valor Realizado</t>
-  </si>
-  <si>
-    <t>Consultor Interno</t>
-  </si>
-  <si>
-    <t>Representante-pedido</t>
-  </si>
-  <si>
-    <t>Tipo de Mercadoria</t>
-  </si>
-  <si>
-    <t>Subgrupo</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Negócio</t>
-  </si>
-  <si>
-    <t>Fabricante</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>BBB</t>
-  </si>
-  <si>
-    <t>TESTE</t>
-  </si>
-  <si>
-    <t>TESTE2</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>SAMANTA</t>
-  </si>
-  <si>
-    <t>DENER.MARTINS</t>
-  </si>
-  <si>
-    <t>Mateus Machado</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>EXO</t>
-  </si>
-  <si>
-    <t>IQ Standard</t>
-  </si>
-  <si>
-    <t>Sonda Serie EXO</t>
-  </si>
-  <si>
-    <t>Medidor de Vazão Fixo</t>
-  </si>
-  <si>
-    <t>Hidrologia</t>
-  </si>
-  <si>
-    <t>YSI</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -144,36 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,148 +424,249 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código Produto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição Produto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dt Emissão</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Realizado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Representante-pedido</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Mercadoria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Subgrupo</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Negócio</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fabricante</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ITEM 5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SAMANTA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Mateus Machado</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EXO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sonda Serie EXO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Hidrologia</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BBB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ITEM 6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SAMANTA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mateus Machado</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IQ Standard</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Medidor de Vazão Fixo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Hidrologia</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YSI</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ITEM 7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TESTE2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>45941</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DENER.MARTINS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Mateus Machado</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EXO</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sonda Serie EXO</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Hidrologia</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Faturados_YTD.xlsx
+++ b/Faturados_YTD.xlsx
@@ -1,40 +1,144 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+  <si>
+    <t>Código Produto</t>
+  </si>
+  <si>
+    <t>Descrição Produto</t>
+  </si>
+  <si>
+    <t>Processo</t>
+  </si>
+  <si>
+    <t>Dt Emissão</t>
+  </si>
+  <si>
+    <t>Valor Realizado</t>
+  </si>
+  <si>
+    <t>Consultor Interno</t>
+  </si>
+  <si>
+    <t>Representante-pedido</t>
+  </si>
+  <si>
+    <t>Tipo de Mercadoria</t>
+  </si>
+  <si>
+    <t>Subgrupo</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Negócio</t>
+  </si>
+  <si>
+    <t>Fabricante</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>BBB</t>
+  </si>
+  <si>
+    <t>ITEM 5</t>
+  </si>
+  <si>
+    <t>ITEM 6</t>
+  </si>
+  <si>
+    <t>ITEM 7</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>TESTE2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>Mateus Machado</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>IQ Standard</t>
+  </si>
+  <si>
+    <t>Sonda Serie EXO</t>
+  </si>
+  <si>
+    <t>Medidor de Vazão Fixo</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
+  </si>
+  <si>
+    <t>YSI</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +153,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -424,249 +470,157 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Código Produto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descrição Produto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Dt Emissão</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Realizado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Representante-pedido</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Mercadoria</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Subgrupo</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Negócio</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fabricante</t>
-        </is>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ITEM 5</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2">
         <v>45931</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SAMANTA</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mateus Machado</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>EXO</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Sonda Serie EXO</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Hidrologia</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BBB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ITEM 6</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2">
         <v>45931</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>SAMANTA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Mateus Machado</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>IQ Standard</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Medidor de Vazão Fixo</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Hidrologia</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>YSI</t>
-        </is>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ITEM 7</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TESTE2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
         <v>45941</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DENER.MARTINS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Mateus Machado</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>EXO</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Sonda Serie EXO</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Hidrologia</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>